--- a/CBT_2026_3회/산업안전기사_2026_3회_문항등록.xlsx
+++ b/CBT_2026_3회/산업안전기사_2026_3회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1471,17 +1471,17 @@
       </c>
       <c r="AG3" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;업무의 계속성 유지&lt;/strong&gt;는 O.J.T 의 장점이다. Off.J.T 는 일터를 떠나 따로 모여 배우므로 그동안 &lt;strong&gt;일이 끊긴다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;O.J.T 와 Off.J.T&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;O.J.T&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off.J.T&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일터를 떠나 한자리에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가 가르치나&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;직속 상사&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;외부 전문가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;인원&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;개별 · 소수&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다수 동시&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;맞춤&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개인에 맞출 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일률적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;업무&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끊기지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;끊긴다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;시설·교재&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제한적&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 시설을 쓴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;업무의 계속성 유지&lt;/strong&gt;는 O.J.T의 장점이다. Off.J.T는 일터를 떠나 따로 모여 배우므로 그동안 &lt;strong&gt;일이 끊긴다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;O.J.T와 Off.J.T&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;O.J.T&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off.J.T&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일터를 떠나 한자리에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가 가르치나&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;직속 상사&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;외부 전문가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;인원&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;개별 · 소수&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다수 동시&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;맞춤&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개인에 맞출 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일률적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;업무&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끊기지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;끊긴다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;시설·교재&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제한적&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 시설을 쓴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH3" s="32" t="inlineStr">
         <is>
-          <t>② 외부 전문가를 강사로 쓰는 것은 Off.J.T 의 장점이다.&lt;br&gt;③ 특별교재와 시설을 쓸 수 있는 것도 Off.J.T 다.&lt;br&gt;④ 다수에게 조직적으로 가르치는 것도 Off.J.T 다.</t>
+          <t>② 외부 전문가를 강사로 쓰는 것은 Off.J.T의 장점이다.&lt;br&gt;③ 특별교재와 시설을 쓸 수 있는 것도 Off.J.T다.&lt;br&gt;④ 다수에게 조직적으로 가르치는 것도 Off.J.T다.</t>
         </is>
       </c>
       <c r="AI3" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;O.J.T(직장 내 교육)와 Off.J.T(직장 외 교육)&lt;/strong&gt;&lt;br&gt;가르는 기준은 &lt;strong&gt;일을 하면서 배우는가&lt;/strong&gt;다. 일하며 배우면 개별 지도와 업무 지속이 되고, 떠나서 배우면 전문 강사와 시설을 쓸 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;O.J.T 는 개별·계속, Off.J.T 는 다수·전문&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;O.J.T(직장 내 교육)와 Off.J.T(직장 외 교육)&lt;/strong&gt;&lt;br&gt;가르는 기준은 &lt;strong&gt;일을 하면서 배우는가&lt;/strong&gt;다. 일하며 배우면 개별 지도와 업무 지속이 되고, 떠나서 배우면 전문 강사와 시설을 쓸 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;O.J.T는 개별·계속, Off.J.T는 다수·전문&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="AI5" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;구안법(Project Method)&lt;/strong&gt;&lt;br&gt;구안법은 &lt;strong&gt;학습자가 스스로 목표를 세우고 실행&lt;/strong&gt; 하는 방법이다. 강사가 정해 주는 강의식과 정반대 자리에 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;목 · 계 · 활 · 평&lt;/u&gt; — 목적 결정, 계획 수립, 활동, 평가.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;구안법(Project Method)&lt;/strong&gt;&lt;br&gt;구안법은 &lt;strong&gt;학습자가 스스로 목표를 세우고 실행&lt;/strong&gt;하는 방법이다. 강사가 정해 주는 강의식과 정반대 자리에 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;목 · 계 · 활 · 평&lt;/u&gt; — 목적 결정, 계획 수립, 활동, 평가.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AG7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;대책선정의 원칙&lt;/strong&gt;은 하인리히 &lt;strong&gt;사고예방 5단계&lt;/strong&gt;의 셋째 단계에 나오는 말이다. 무재해 운동 3원칙에는 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;무재해 운동의 3원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무(無)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;재해는 0 이 목표가 아니라 &lt;u&gt;잠재 위험까지 없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;단순히 사고가 없는 상태가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;선취(先取)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사고가 나기 전에&lt;/u&gt; 위험을 찾아 없앤다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「안전제일」의 원칙&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;참가(參加)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원이 문제 해결에 참여&lt;/u&gt; 한다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「참여」가 아니라 「참가」&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;대책선정의 원칙&lt;/strong&gt;은 하인리히 &lt;strong&gt;사고예방 5단계&lt;/strong&gt;의 셋째 단계에 나오는 말이다. 무재해 운동 3원칙에는 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;무재해 운동의 3원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무(無)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;재해는 0이 목표가 아니라 &lt;u&gt;잠재 위험까지 없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;단순히 사고가 없는 상태가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;선취(先取)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사고가 나기 전에&lt;/u&gt; 위험을 찾아 없앤다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「안전제일」의 원칙&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;참가(參加)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원이 문제 해결에 참여&lt;/u&gt; 한다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「참여」가 아니라 「참가」&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH7" s="32" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AH8" s="32" t="inlineStr">
         <is>
-          <t>② 브레인스토밍은 자유롭게 의견을 내는 회의 기법이다.&lt;br&gt;③ ECR(Error Cause Removal)은 근로자가 오류 원인을 스스로 제안하는 제도다.&lt;br&gt;④ STOP 은 듀폰이 만든 관찰 중심의 안전훈련 프로그램이다.</t>
+          <t>② 브레인스토밍은 자유롭게 의견을 내는 회의 기법이다.&lt;br&gt;③ ECR(Error Cause Removal)은 근로자가 오류 원인을 스스로 제안하는 제도다.&lt;br&gt;④ STOP은 듀폰이 만든 관찰 중심의 안전훈련 프로그램이다.</t>
         </is>
       </c>
       <c r="AI8" s="32" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AI12" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;사업장 규모별 안전관리 조직&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;라인형 100명 미만 → 스태프형 100~1,000명 → 라인·스태프형 1,000명 이상&lt;/strong&gt; 순서로 커진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;100 · 1,000 을 경계로 셋&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;사업장 규모별 안전관리 조직&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;라인형 100명 미만 → 스태프형 100~1,000명 → 라인·스태프형 1,000명 이상&lt;/strong&gt; 순서로 커진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;100 · 1,000을 경계로 셋&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="AG14" s="32" t="inlineStr">
         <is>
-          <t>$B = f ( P \cdot E )$ 다. 행동은 &lt;strong&gt;사람과 환경이 함께 만든&lt;/strong&gt; 결과다.&lt;img src="safe_A_2026_03_012_exp1.png"&gt;&lt;em&gt;레빈의 장 이론 — 행동은 사람과 환경의 함수다&lt;/em&gt;</t>
+          <t>$B = f ( P \cdot E )$다. 행동은 &lt;strong&gt;사람과 환경이 함께 만든&lt;/strong&gt; 결과다.&lt;img src="safe_A_2026_03_012_exp1.png"&gt;&lt;em&gt;레빈의 장 이론 — 행동은 사람과 환경의 함수다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH14" s="32" t="inlineStr">
         <is>
-          <t>② $B = f ( P + 1 ) E$ 라는 식은 없다.&lt;br&gt;③ 좌변은 P 가 아니라 B 다.&lt;br&gt;④ 좌변은 E 가 아니라 B 다.</t>
+          <t>② $B = f ( P + 1 ) E$라는 식은 없다.&lt;br&gt;③ 좌변은 P가 아니라 B다.&lt;br&gt;④ 좌변은 E가 아니라 B다.</t>
         </is>
       </c>
       <c r="AI14" s="32" t="inlineStr">
@@ -3664,17 +3664,17 @@
       </c>
       <c r="AG20" s="32" t="inlineStr">
         <is>
-          <t>전체는 $1 + 29 + 300 = 330$ 건이다. $29 / 330 \times 100 \fallingdotseq 8.8$ [%] 다.&lt;img src="safe_A_2026_03_018_exp1.png"&gt;&lt;em&gt;하인리히 1 : 29 : 300 — 큰 사고 하나 밑에 300건의 아차사고가 있다&lt;/em&gt;</t>
+          <t>전체는 $1 + 29 + 300 = 330$ 건이다. $29 / 330 \times 100 \fallingdotseq 8.8$ [%]다.&lt;img src="safe_A_2026_03_018_exp1.png"&gt;&lt;em&gt;하인리히 1 : 29 : 300 — 큰 사고 하나 밑에 300건의 아차사고가 있다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
-          <t>② 9.8 [%] 는 분모를 잘못 잡았을 때 나온다.&lt;br&gt;③ 10.8 [%] 도 맞지 않는다.&lt;br&gt;④ 11.8 [%] 도 맞지 않는다.</t>
+          <t>② 9.8 [%]는 분모를 잘못 잡았을 때 나온다.&lt;br&gt;③ 10.8 [%] 도 맞지 않는다.&lt;br&gt;④ 11.8 [%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI20" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하인리히의 1 : 29 : 300 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;중상 1 · 경상 29 · 무상해사고 300&lt;/strong&gt;이다. 버드는 &lt;strong&gt;1 : 10 : 30 : 600&lt;/strong&gt;으로 &lt;strong&gt;물적 손실만 있는 사고 30&lt;/strong&gt;을 따로 세웠다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;330 이 분모&lt;/u&gt; — 1은 0.3 [%], 29는 8.8 [%], 300은 90.9 [%].&lt;/p&gt;</t>
+          <t>&lt;strong&gt;하인리히의 1 : 29 : 300 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;중상 1 · 경상 29 · 무상해사고 300&lt;/strong&gt;이다. 버드는 &lt;strong&gt;1 : 10 : 30 : 600&lt;/strong&gt;으로 &lt;strong&gt;물적 손실만 있는 사고 30&lt;/strong&gt;을 따로 세웠다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;330이 분모&lt;/u&gt; — 1은 0.3 [%], 29는 8.8 [%], 300은 90.9 [%].&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AI22" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;재해조사의 목적&lt;/strong&gt;&lt;br&gt;조사할 때는 &lt;strong&gt;사실을 있는 그대로 · 신속하게 · 여러 사람이 · 책임 추궁보다 원인 규명을 앞세워&lt;/strong&gt; 한다. 이 넷이 재해조사의 원칙이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;원인을 묻지 사람을 묻지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;재해조사의 목적&lt;/strong&gt;&lt;br&gt;조사할 때는 &lt;strong&gt;사실을 있는 그대로 · 신속하게 · 여러 사람이 · 책임 추궁보다 원인 규명을 앞세워&lt;/strong&gt;한다. 이 넷이 재해조사의 원칙이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;원인을 묻지 사람을 묻지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
-          <t>① Command error 는 필요한 정보나 지시가 없어 생기는 오류다.&lt;br&gt;③ Secondary error 는 다른 오류에서 파생된 2차 오류다.&lt;br&gt;④ Commission error 는 하기는 했으나 잘못한 오류다.</t>
+          <t>① Command error는 필요한 정보나 지시가 없어 생기는 오류다.&lt;br&gt;③ Secondary error는 다른 오류에서 파생된 2차 오류다.&lt;br&gt;④ Commission error는 하기는 했으나 잘못한 오류다.</t>
         </is>
       </c>
       <c r="AI23" s="32" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
-          <t>① NOR 은 OR 의 결과를 뒤집는다.&lt;br&gt;② AND 는 입력이 모두 일어나야 출력이 난다.&lt;br&gt;④ NAND 는 AND 의 결과를 뒤집는다.</t>
+          <t>① NOR은 OR의 결과를 뒤집는다.&lt;br&gt;② AND는 입력이 모두 일어나야 출력이 난다.&lt;br&gt;④ NAND는 AND의 결과를 뒤집는다.</t>
         </is>
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 논리 게이트&lt;/strong&gt;&lt;br&gt;확률로 보면 &lt;strong&gt;OR 은 더하고(&lt;/strong&gt;$1 - \prod ( 1 - q_{i} )$&lt;strong&gt;), AND 는 곱한다(&lt;/strong&gt;$\prod q_{i}$&lt;strong&gt;)&lt;/strong&gt;. 그래서 &lt;strong&gt;AND 로 묶인 구조가 훨씬 안전하다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하나만 나도 OR, 다 나야 AND&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 논리 게이트&lt;/strong&gt;&lt;br&gt;확률로 보면 &lt;strong&gt;OR은 더하고(&lt;/strong&gt;$1 - \prod ( 1 - q_{i} )$&lt;strong&gt;), AND는 곱한다(&lt;/strong&gt;$\prod q_{i}$&lt;strong&gt;)&lt;/strong&gt;. 그래서 &lt;strong&gt;AND로 묶인 구조가 훨씬 안전하다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하나만 나도 OR, 다 나야 AND&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="AG26" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;결함사상&lt;/strong&gt;이다. 사각형으로 그리며 &lt;strong&gt;고장이냐 정상이냐 두 상태 가운데 고장 쪽&lt;/strong&gt;을 가리킨다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 사상 기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇인가&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;결함사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 상태 가운데 고장 쪽&lt;/u&gt; — 개별 결함&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기본사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 이상 나눌 수 없는 &lt;u&gt;맨 밑의 원인&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통상사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;집 모양&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상 운전 중에도 &lt;u&gt;늘 일어나는&lt;/u&gt; 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;생략사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;마름모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정보가 없어 &lt;u&gt;더 전개하지 않는&lt;/u&gt; 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전이기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;삼각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 곳으로 &lt;u&gt;이어짐&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;결함사상&lt;/strong&gt;이다. 사각형으로 그리며 &lt;strong&gt;고장이냐 정상이냐 두 상태 가운데 고장 쪽&lt;/strong&gt;을 가리킨다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 사상 기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇인가&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;결함사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 상태 가운데 고장 쪽&lt;/u&gt; — 개별 결함&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기본사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 이상 나눌 수 없는 &lt;u&gt;맨 밑의 원인&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;통상사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;집 모양&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상 운전 중에도 &lt;u&gt;늘 일어나는&lt;/u&gt; 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;생략사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;마름모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정보가 없어 &lt;u&gt;더 전개하지 않는&lt;/u&gt; 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전이기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;삼각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 곳으로 &lt;u&gt;이어짐&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH26" s="32" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AI26" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 사상 기호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;네모는 결함, 동그라미는 기본&lt;/strong&gt; 이라고 새긴다. 도면을 그릴 때 맨 위 톱사상도 사각형으로 그린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;결함은 네모, 기본은 원, 생략은 마름모&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 사상 기호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;네모는 결함, 동그라미는 기본&lt;/strong&gt; 이라고 새긴다. 도면을 그릴 때 맨 위 톱사상도 사각형으로 그린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;결함은 네모, 기본은 원, 생략은 마름모&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="AH27" s="32" t="inlineStr">
         <is>
-          <t>② Mistake 는 의도 자체가 잘못된 경우다.&lt;br&gt;③ Lapse 는 기억이 빠져 단계를 건너뛴 경우다.&lt;br&gt;④ Violation 은 알면서 규칙을 어긴 경우다.</t>
+          <t>② Mistake는 의도 자체가 잘못된 경우다.&lt;br&gt;③ Lapse는 기억이 빠져 단계를 건너뛴 경우다.&lt;br&gt;④ Violation은 알면서 규칙을 어긴 경우다.</t>
         </is>
       </c>
       <c r="AI27" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;라스무센(Rasmussen)과 리즌(Reason)의 오류 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Slip 과 Lapse 는 계획이 옳고 실행이 어긋난 것&lt;/strong&gt;, &lt;strong&gt;Mistake 는 계획 자체가 틀린 것&lt;/strong&gt;, &lt;strong&gt;Violation 은 고의&lt;/strong&gt;다. 앞의 셋은 교육과 설계로, 마지막은 관리로 다룬다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;의도가 맞으면 Slip, 의도가 틀리면 Mistake&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;라스무센(Rasmussen)과 리즌(Reason)의 오류 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Slip과 Lapse는 계획이 옳고 실행이 어긋난 것&lt;/strong&gt;, &lt;strong&gt;Mistake는 계획 자체가 틀린 것&lt;/strong&gt;, &lt;strong&gt;Violation은 고의&lt;/strong&gt;다. 앞의 셋은 교육과 설계로, 마지막은 관리로 다룬다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;의도가 맞으면 Slip, 의도가 틀리면 Mistake&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4930,17 +4930,17 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;치명도 분석(CA, Criticality Analysis)&lt;/strong&gt;이다. &lt;strong&gt;얼마나 치명적인가&lt;/strong&gt;로 고장을 줄 세운다. FMEA 와 짝을 지어 &lt;strong&gt;FMECA&lt;/strong&gt;로 쓴다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 위험분석 기법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 보나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PHA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;예비위험분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맨 처음&lt;/u&gt; 개략적으로 위험을 훑는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FHA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;결함위험분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분담 제작&lt;/u&gt; 하는 부분 시스템 사이의 위험&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FMEA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장형태와 영향분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장이 &lt;u&gt;어떤 영향&lt;/u&gt;을 미치나 — 정성적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;CA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;치명도 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 치명적인가&lt;/u&gt; — 정량적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ETA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사건수 분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;초기 사건 뒤 &lt;u&gt;무슨 일이 이어지나&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FTA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;결함수 분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;결과에서 &lt;u&gt;원인으로 거슬러&lt;/u&gt; 올라간다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;치명도 분석(CA, Criticality Analysis)&lt;/strong&gt;이다. &lt;strong&gt;얼마나 치명적인가&lt;/strong&gt;로 고장을 줄 세운다. FMEA와 짝을 지어 &lt;strong&gt;FMECA&lt;/strong&gt;로 쓴다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 위험분석 기법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 보나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PHA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;예비위험분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맨 처음&lt;/u&gt; 개략적으로 위험을 훑는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FHA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;결함위험분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분담 제작&lt;/u&gt;하는 부분 시스템 사이의 위험&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FMEA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장형태와 영향분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장이 &lt;u&gt;어떤 영향&lt;/u&gt;을 미치나 — 정성적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;CA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;치명도 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얼마나 치명적인가&lt;/u&gt; — 정량적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ETA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사건수 분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;초기 사건 뒤 &lt;u&gt;무슨 일이 이어지나&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FTA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;결함수 분석&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;결과에서 &lt;u&gt;원인으로 거슬러&lt;/u&gt; 올라간다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
-          <t>② ETA 는 초기 사건 뒤의 전개를 따라가는 기법이다.&lt;br&gt;③ FHA 는 분담 제작하는 부분 시스템 사이의 위험을 보는 기법이다.&lt;br&gt;④ FTA 는 결과에서 원인으로 거슬러 올라가는 기법이다.</t>
+          <t>② ETA는 초기 사건 뒤의 전개를 따라가는 기법이다.&lt;br&gt;③ FHA는 분담 제작하는 부분 시스템 사이의 위험을 보는 기법이다.&lt;br&gt;④ FTA는 결과에서 원인으로 거슬러 올라가는 기법이다.</t>
         </is>
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;치명도 분석(CA)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FMEA 는 「어떤 영향」, CA 는 「얼마나 치명적」&lt;/strong&gt;이다. 둘을 합친 FMECA 가 실무에서 쓰인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;치명도를 재면 CA&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;치명도 분석(CA)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FMEA는 「어떤 영향」, CA는 「얼마나 치명적」&lt;/strong&gt;이다. 둘을 합친 FMECA가 실무에서 쓰인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;치명도를 재면 CA&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5059,17 +5059,17 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA&lt;/strong&gt;다. &lt;strong&gt;고장 형태(Failure Mode)&lt;/strong&gt;라는 말이 나오면 FMEA 로 보면 된다.</t>
+          <t>&lt;strong&gt;FMEA&lt;/strong&gt;다. &lt;strong&gt;고장 형태(Failure Mode)&lt;/strong&gt;라는 말이 나오면 FMEA로 보면 된다.</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① ETA 는 초기 사건에서 결과로 따라 내려가는 기법이다.&lt;br&gt;② HEA 는 인간의 오류를 분석하는 기법이다.&lt;br&gt;③ PHA 는 설계 초기에 개략적으로 위험을 훑는 기법이다.</t>
+          <t>① ETA는 초기 사건에서 결과로 따라 내려가는 기법이다.&lt;br&gt;② HEA는 인간의 오류를 분석하는 기법이다.&lt;br&gt;③ PHA는 설계 초기에 개략적으로 위험을 훑는 기법이다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA(고장형태와 영향분석)&lt;/strong&gt;&lt;br&gt;FMEA 는 &lt;strong&gt;귀납적이고 정성적&lt;/strong&gt;이며 &lt;strong&gt;밑에서 위로&lt;/strong&gt; 올라간다. FTA 는 &lt;strong&gt;연역적이고 정량적&lt;/strong&gt;이며 &lt;strong&gt;위에서 아래로&lt;/strong&gt; 내려간다. 방향이 정반대다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;「고장 형태」가 나오면 FMEA&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FMEA(고장형태와 영향분석)&lt;/strong&gt;&lt;br&gt;FMEA는 &lt;strong&gt;귀납적이고 정성적&lt;/strong&gt;이며 &lt;strong&gt;밑에서 위로&lt;/strong&gt; 올라간다. FTA는 &lt;strong&gt;연역적이고 정량적&lt;/strong&gt;이며 &lt;strong&gt;위에서 아래로&lt;/strong&gt; 내려간다. 방향이 정반대다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;「고장 형태」가 나오면 FMEA&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="AG32" s="32" t="inlineStr">
         <is>
-          <t>평균 10,000, 표준편차 200 이다. $Z = ( 9 {,} 600 - 10 {,} 000 ) / 200 =-2$ 다. 9,600시간을 &lt;strong&gt;넘겨 살아 있을 확률&lt;/strong&gt;이므로 $R = P ( Z &amp;gt; - 2 ) = P ( Z \le 2 ) = 0.9772$ 다.</t>
+          <t>평균 10,000, 표준편차 200이다. $Z = ( 9 {,} 600 - 10 {,} 000 ) / 200 =-2$다. 9,600시간을 &lt;strong&gt;넘겨 살아 있을 확률&lt;/strong&gt;이므로 $R = P ( Z &amp;gt; - 2 ) = P ( Z \le 2 ) = 0.9772$다.</t>
         </is>
       </c>
       <c r="AH32" s="32" t="inlineStr">
         <is>
-          <t>① 84.13 [%] 는 $Z =-1$ 일 때다.&lt;br&gt;② 93.32 [%] 는 $Z =-1.5$ 일 때다.&lt;br&gt;④ 99.87 [%] 는 $Z =-3$ 일 때다.</t>
+          <t>① 84.13 [%]는 $Z =-1$일 때다.&lt;br&gt;② 93.32 [%]는 $Z =-1.5$일 때다.&lt;br&gt;④ 99.87 [%]는 $Z =-3$일 때다.</t>
         </is>
       </c>
       <c r="AI32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정규분포를 따르는 수명의 신뢰도&lt;/strong&gt;&lt;br&gt;신뢰도는 &lt;strong&gt;그 시각까지 고장 나지 않을 확률&lt;/strong&gt;이다. $Z$ 가 음수로 나오면 &lt;strong&gt;정규분포가 좌우대칭&lt;/strong&gt;이므로 부호를 떼고 표를 그대로 읽으면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Z = ( t - \mu ) / \sigma$ — &lt;u&gt;음수면 대칭으로 뒤집는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정규분포를 따르는 수명의 신뢰도&lt;/strong&gt;&lt;br&gt;신뢰도는 &lt;strong&gt;그 시각까지 고장 나지 않을 확률&lt;/strong&gt;이다. $Z$가 음수로 나오면 &lt;strong&gt;정규분포가 좌우대칭&lt;/strong&gt;이므로 부호를 떼고 표를 그대로 읽으면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Z = ( t - \mu ) / \sigma$ — &lt;u&gt;음수면 대칭으로 뒤집는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5321,12 +5321,12 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>0.95 짜리 하나가 앞에 직렬로 있고, 그 뒤에 0.95 와 0.90 이 병렬로 붙어 있다. 병렬은 $1 - ( 1 - 0.95 ) ( 1 - 0.90 ) = 0.995$ 이고, 전체는 $0.95 \times 0.995 \fallingdotseq 0.9453$ 이다.&lt;img src="safe_A_2026_03_031_exp1.png"&gt;&lt;em&gt;직렬 하나 뒤에 병렬 둘 — 병렬을 먼저 묶고 곱한다&lt;/em&gt;</t>
+          <t>0.95 짜리 하나가 앞에 직렬로 있고, 그 뒤에 0.95와 0.90이 병렬로 붙어 있다. 병렬은 $1 - ( 1 - 0.95 ) ( 1 - 0.90 ) = 0.995$이고, 전체는 $0.95 \times 0.995 \fallingdotseq 0.9453$이다.&lt;img src="safe_A_2026_03_031_exp1.png"&gt;&lt;em&gt;직렬 하나 뒤에 병렬 둘 — 병렬을 먼저 묶고 곱한다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① 0.8123 은 셋을 모두 직렬로 곱했을 때에 가깝다.&lt;br&gt;③ 0.9553 은 병렬 계산이 어긋난 값이다.&lt;br&gt;④ 0.9953 은 직렬 부품을 빼먹고 병렬만 구한 값에 가깝다.</t>
+          <t>① 0.8123은 셋을 모두 직렬로 곱했을 때에 가깝다.&lt;br&gt;③ 0.9553은 병렬 계산이 어긋난 값이다.&lt;br&gt;④ 0.9953은 직렬 부품을 빼먹고 병렬만 구한 값에 가깝다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
@@ -5450,17 +5450,17 @@
       </c>
       <c r="AG34" s="32" t="inlineStr">
         <is>
-          <t>배기량은 $90 / 5 = 18$ [L/min] 이다. 질소는 몸에 쓰이지 않으므로 그 양으로 흡기량을 되돌린다. 배기 질소는 $100 - 16 - 4 = 80$ [%] 이므로 $V_{1} = 18 \times 0.80 / 0.79 = 18.228$ [L/min] 이다. 산소소비량은 $18.228 \times 0.21 - 18 \times 0.16 = 3.828 - 2.88 \fallingdotseq 0.948$ [L/min] 이다.</t>
+          <t>배기량은 $90 / 5 = 18$ [L/min]이다. 질소는 몸에 쓰이지 않으므로 그 양으로 흡기량을 되돌린다. 배기 질소는 $100 - 16 - 4 = 80$ [%]이므로 $V_{1} = 18 \times 0.80 / 0.79 = 18.228$ [L/min]이다. 산소소비량은 $18.228 \times 0.21 - 18 \times 0.16 = 3.828 - 2.88 \fallingdotseq 0.948$ [L/min]이다.</t>
         </is>
       </c>
       <c r="AH34" s="32" t="inlineStr">
         <is>
-          <t>② 1.948 은 흡기량 보정을 빼먹었을 때에 가깝다.&lt;br&gt;③ 4.74 는 5로 나누지 않았을 때 나온다.&lt;br&gt;④ 5.74 도 자릿수가 어긋난다.</t>
+          <t>② 1.948은 흡기량 보정을 빼먹었을 때에 가깝다.&lt;br&gt;③ 4.74는 5로 나누지 않았을 때 나온다.&lt;br&gt;④ 5.74 도 자릿수가 어긋난다.</t>
         </is>
       </c>
       <c r="AI34" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산소소비량의 계산&lt;/strong&gt;&lt;br&gt;핵심은 &lt;strong&gt;질소는 소비되지도 생성되지도 않는다&lt;/strong&gt;는 점이다. 그래서 &lt;strong&gt;질소량이 같다&lt;/strong&gt;는 조건으로 흡기량을 되찾는다. 산소소비량 1 [L] 은 약 &lt;strong&gt;5 [kcal]&lt;/strong&gt;의 에너지에 해당한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;질소로 흡기량을 되찾는다&lt;/u&gt; — $V_{1} = V_{2} \times N_{2} / 79$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;산소소비량의 계산&lt;/strong&gt;&lt;br&gt;핵심은 &lt;strong&gt;질소는 소비되지도 생성되지도 않는다&lt;/strong&gt;는 점이다. 그래서 &lt;strong&gt;질소량이 같다&lt;/strong&gt;는 조건으로 흡기량을 되찾는다. 산소소비량 1 [L]은 약 &lt;strong&gt;5 [kcal]&lt;/strong&gt;의 에너지에 해당한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;질소로 흡기량을 되찾는다&lt;/u&gt; — $V_{1} = V_{2} \times N_{2} / 79$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="AI36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;실효온도(감각온도)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;실효온도는 셋, 수정 실효온도는 넷&lt;/strong&gt;이다. 옥외 작업의 WBGT 에 건구온도가 들어가는 것과 같은 이치로, &lt;strong&gt;햇볕(복사열)이 있으면 항목이 하나 늘어난다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;실효온도에 복사열은 없다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;실효온도(감각온도)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;실효온도는 셋, 수정 실효온도는 넷&lt;/strong&gt;이다. 옥외 작업의 WBGT에 건구온도가 들어가는 것과 같은 이치로, &lt;strong&gt;햇볕(복사열)이 있으면 항목이 하나 늘어난다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;실효온도에 복사열은 없다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;조명 방식의 분류&lt;/strong&gt;&lt;br&gt;국소조명만 쓰면 주변이 어두워 &lt;strong&gt;눈이 자꾸 명순응·암순응을 되풀이하며 피로해진다&lt;/strong&gt;. 그래서 실무에서는 &lt;strong&gt;전반조명과 국소조명을 함께&lt;/strong&gt; 쓰고, &lt;strong&gt;국소 : 전반 = 10 : 1 을 넘지 않게&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;필요한 곳만 밝히면 국소조명&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;조명 방식의 분류&lt;/strong&gt;&lt;br&gt;국소조명만 쓰면 주변이 어두워 &lt;strong&gt;눈이 자꾸 명순응·암순응을 되풀이하며 피로해진다&lt;/strong&gt;. 그래서 실무에서는 &lt;strong&gt;전반조명과 국소조명을 함께&lt;/strong&gt; 쓰고, &lt;strong&gt;국소 : 전반 = 10 : 1을 넘지 않게&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;필요한 곳만 밝히면 국소조명&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AG38" s="32" t="inlineStr">
         <is>
-          <t>너무 밝거나 &lt;strong&gt;암순응이 필요한 곳에서는 눈을 쓰기 어렵다&lt;/strong&gt;. 이때는 귀로 알리는 편이 낫다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;청각과 시각, 어느 쪽이 유리한가&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상황&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;청각&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;시각&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;메시지가 &lt;u&gt;짧고 간단&lt;/u&gt; 하다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;메시지가 &lt;u&gt;길고 복잡&lt;/u&gt; 하다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;즉각 반응&lt;/u&gt;이 필요하다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;나중에 &lt;u&gt;다시 참조&lt;/u&gt; 한다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;공간적 위치&lt;/u&gt;를 다룬다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시간의 흐름&lt;/u&gt;을 다룬다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;수신자가 &lt;u&gt;돌아다닌다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;수신 장소가 &lt;u&gt;너무 시끄럽다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;너무 밝거나 암순응&lt;/u&gt;이 필요하다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>너무 밝거나 &lt;strong&gt;암순응이 필요한 곳에서는 눈을 쓰기 어렵다&lt;/strong&gt;. 이때는 귀로 알리는 편이 낫다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;청각과 시각, 어느 쪽이 유리한가&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상황&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;청각&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;시각&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;메시지가 &lt;u&gt;짧고 간단&lt;/u&gt;하다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;메시지가 &lt;u&gt;길고 복잡&lt;/u&gt;하다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;즉각 반응&lt;/u&gt;이 필요하다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;나중에 &lt;u&gt;다시 참조&lt;/u&gt;한다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;공간적 위치&lt;/u&gt;를 다룬다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시간의 흐름&lt;/u&gt;을 다룬다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;수신자가 &lt;u&gt;돌아다닌다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;수신 장소가 &lt;u&gt;너무 시끄럽다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;너무 밝거나 암순응&lt;/u&gt;이 필요하다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;○&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH38" s="32" t="inlineStr">
@@ -6095,17 +6095,17 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>1,000 [Hz] 에서는 &lt;strong&gt;dB = phon&lt;/strong&gt;이다. $\mathrm{sone} = 2^{( \mathrm{phon} - 40 ) / 10}$ 이므로 60 [phon] 은 $2^{2} = 4$ [sone] 이다. 4배면 16 [sone] 이고, $16 = 2^{4}$ 이므로 $\mathrm{phon} = 40 + 40 = 80$ 이다.</t>
+          <t>1,000 [Hz] 에서는 &lt;strong&gt;dB = phon&lt;/strong&gt;이다. $\mathrm{sone} = 2^{( \mathrm{phon} - 40 ) / 10}$이므로 60 [phon]은 $2^{2} = 4$ [sone]이다. 4배면 16 [sone]이고, $16 = 2^{4}$이므로 $\mathrm{phon} = 40 + 40 = 80$이다.</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
-          <t>① 70 [dB] 는 8 [sone] 으로 2배다.&lt;br&gt;③ 90 [dB] 는 32 [sone] 으로 8배다.&lt;br&gt;④ 100 [dB] 는 64 [sone] 으로 16배다.</t>
+          <t>① 70 [dB]는 8 [sone]으로 2배다.&lt;br&gt;③ 90 [dB]는 32 [sone]으로 8배다.&lt;br&gt;④ 100 [dB]는 64 [sone]으로 16배다.</t>
         </is>
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;phon 과 sone&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;10 [phon] 이 오를 때마다 sone 은 두 배&lt;/strong&gt;가 된다. 「몇 배 크게 들린다」는 문제는 반드시 &lt;strong&gt;sone&lt;/strong&gt;으로 옮겨 풀어야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;10 phon 오르면 크기는 2배&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;phon과 sone&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;10 [phon]이 오를 때마다 sone은 두 배&lt;/strong&gt;가 된다. 「몇 배 크게 들린다」는 문제는 반드시 &lt;strong&gt;sone&lt;/strong&gt;으로 옮겨 풀어야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;10 phon 오르면 크기는 2배&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6224,17 +6224,17 @@
       </c>
       <c r="AG40" s="32" t="inlineStr">
         <is>
-          <t>총 가동시간은 $1 {,} 000 \times 100 {,} 000 = 10^{8}$ 시간이다. 고장이 5개이므로 $\mathrm{MTTF} = 10^{8} / 5 = 2 \times 10^{7}$ 시간이다.&lt;img src="safe_A_2026_03_038_exp1.png"&gt;&lt;em&gt;MTBF · MTTF · MTTR 의 관계&lt;/em&gt;</t>
+          <t>총 가동시간은 $1 {,} 000 \times 100 {,} 000 = 10^{8}$ 시간이다. 고장이 5개이므로 $\mathrm{MTTF} = 10^{8} / 5 = 2 \times 10^{7}$ 시간이다.&lt;img src="safe_A_2026_03_038_exp1.png"&gt;&lt;em&gt;MTBF · MTTF · MTTR의 관계&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH40" s="32" t="inlineStr">
         <is>
-          <t>① $1 \times 10^{6}$ 은 계산과 맞지 않는다.&lt;br&gt;③ $1 \times 10^{8}$ 은 고장 개수로 나누지 않은 총 가동시간이다.&lt;br&gt;④ $2 \times 10^{9}$ 은 자릿수가 어긋난다.</t>
+          <t>① $1 \times 10^{6}$은 계산과 맞지 않는다.&lt;br&gt;③ $1 \times 10^{8}$은 고장 개수로 나누지 않은 총 가동시간이다.&lt;br&gt;④ $2 \times 10^{9}$은 자릿수가 어긋난다.</t>
         </is>
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;MTTF(평균 고장시간)&lt;/strong&gt;&lt;br&gt;$\mathrm{MTTF} = \text{총 가동시간} \div \text{고장 개수}$ 이고 $\lambda = 1 / \mathrm{MTTF}$ 다. &lt;strong&gt;MTTF 는 고치지 못하는 부품&lt;/strong&gt;, &lt;strong&gt;MTBF 는 고쳐 쓰는 설비&lt;/strong&gt;에 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;총 시간을 고장 수로 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;MTTF(평균 고장시간)&lt;/strong&gt;&lt;br&gt;$\mathrm{MTTF} = \text{총 가동시간} \div \text{고장 개수}$이고 $\lambda = 1 / \mathrm{MTTF}$다. &lt;strong&gt;MTTF는 고치지 못하는 부품&lt;/strong&gt;, &lt;strong&gt;MTBF는 고쳐 쓰는 설비&lt;/strong&gt;에 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;총 시간을 고장 수로 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>정량적 평가 항목은 &lt;strong&gt;취급물질 · 화학설비의 용량 · 온도 · 압력 · 조작&lt;/strong&gt; 다섯이다. &lt;strong&gt;훈련&lt;/strong&gt;은 여기 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;화학설비 안전성 평가 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;관계 자료의 정비 검토&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설계도 · 공정도 · 물질 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입지 조건 · 공장 내 배치 · 건조물 · 소방설비 · 원재료 · 공정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;취급물질 · 용량 · 온도 · 압력 · 조작&lt;/u&gt; — 다섯 항목을 &lt;u&gt;A~D 등급&lt;/u&gt;으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전대책 수립&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비 대책과 관리 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;재해정보에 의한 재평가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;비슷한 사고 사례로 다시 본다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;FTA 에 의한 재평가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 위험한 &lt;u&gt;등급 Ⅰ·Ⅱ&lt;/u&gt;에 적용&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>정량적 평가 항목은 &lt;strong&gt;취급물질 · 화학설비의 용량 · 온도 · 압력 · 조작&lt;/strong&gt; 다섯이다. &lt;strong&gt;훈련&lt;/strong&gt;은 여기 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;화학설비 안전성 평가 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;관계 자료의 정비 검토&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설계도 · 공정도 · 물질 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입지 조건 · 공장 내 배치 · 건조물 · 소방설비 · 원재료 · 공정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;취급물질 · 용량 · 온도 · 압력 · 조작&lt;/u&gt; — 다섯 항목을 &lt;u&gt;A~D 등급&lt;/u&gt;으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전대책 수립&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비 대책과 관리 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;재해정보에 의한 재평가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;비슷한 사고 사례로 다시 본다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;FTA에 의한 재평가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 위험한 &lt;u&gt;등급 Ⅰ·Ⅱ&lt;/u&gt;에 적용&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
@@ -6482,17 +6482,17 @@
       </c>
       <c r="AG42" s="32" t="inlineStr">
         <is>
-          <t>$\text{시각} ( \text{분} ) = \dfrac{57.3 \times 60 \times L}{D}$ 다. $57.3 \times 60 \times 0.03 / 23 = 103.14 / 23 \fallingdotseq 4.48$ 분이다.</t>
+          <t>$\text{시각} ( \text{분} ) = \dfrac{57.3 \times 60 \times L}{D}$다. $57.3 \times 60 \times 0.03 / 23 = 103.14 / 23 \fallingdotseq 4.48$ 분이다.</t>
         </is>
       </c>
       <c r="AH42" s="32" t="inlineStr">
         <is>
-          <t>① 0.001 은 57.3 과 60 을 곱하지 않은 라디안 값 쪽이다.&lt;br&gt;② 0.007 도 환산을 빼먹은 값이다.&lt;br&gt;④ 24.55 는 자릿수가 어긋난다.</t>
+          <t>① 0.001은 57.3과 60을 곱하지 않은 라디안 값 쪽이다.&lt;br&gt;② 0.007 도 환산을 빼먹은 값이다.&lt;br&gt;④ 24.55는 자릿수가 어긋난다.</t>
         </is>
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시각(視角)과 시력&lt;/strong&gt;&lt;br&gt;$\text{시력} = 1 / \text{시각} ( \text{분} )$ 이다. &lt;strong&gt;시각이 작을수록 시력이 좋다&lt;/strong&gt;. 1분(1/60도)을 구별하면 시력 1.0 이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $57.3 \times 60 \times L \div D$ — &lt;u&gt;57.3 은 라디안을 도로, 60 은 도를 분으로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;시각(視角)과 시력&lt;/strong&gt;&lt;br&gt;$\text{시력} = 1 / \text{시각} ( \text{분} )$이다. &lt;strong&gt;시각이 작을수록 시력이 좋다&lt;/strong&gt;. 1분(1/60도)을 구별하면 시력 1.0이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $57.3 \times 60 \times L \div D$ — &lt;u&gt;57.3은 라디안을 도로, 60은 도를 분으로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AG43" s="32" t="inlineStr">
         <is>
-          <t>작은 공작물을 &lt;strong&gt;손으로 잡으면 드릴에 물려 함께 돌아간다&lt;/strong&gt;. &lt;strong&gt;바이스나 클램프로 고정&lt;/strong&gt; 해야 한다.</t>
+          <t>작은 공작물을 &lt;strong&gt;손으로 잡으면 드릴에 물려 함께 돌아간다&lt;/strong&gt;. &lt;strong&gt;바이스나 클램프로 고정&lt;/strong&gt;해야 한다.</t>
         </is>
       </c>
       <c r="AH43" s="32" t="inlineStr">
@@ -6740,17 +6740,17 @@
       </c>
       <c r="AG44" s="32" t="inlineStr">
         <is>
-          <t>$V = \pi D N$ 다. 지름을 [m] 로 바꾸면 $V = \pi \times 0.3 \times 500 \fallingdotseq 471$ [m/min] 이다.</t>
+          <t>$V = \pi D N$다. 지름을 [m]로 바꾸면 $V = \pi \times 0.3 \times 500 \fallingdotseq 471$ [m/min]이다.</t>
         </is>
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
-          <t>② 551 은 계산과 맞지 않는다.&lt;br&gt;③ 751 도 맞지 않는다.&lt;br&gt;④ 1025 는 지름 대신 지름의 두 배를 썼을 때 쪽이다.</t>
+          <t>② 551은 계산과 맞지 않는다.&lt;br&gt;③ 751 도 맞지 않는다.&lt;br&gt;④ 1025는 지름 대신 지름의 두 배를 썼을 때 쪽이다.</t>
         </is>
       </c>
       <c r="AI44" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;원주속도 $V = \pi D N$&lt;/strong&gt;&lt;br&gt;단위를 맞추는 것이 전부다. &lt;strong&gt;[m/min] 이면 D 를 [m] 로&lt;/strong&gt;, &lt;strong&gt;[m/s] 면 &lt;/strong&gt;$\pi D N / 60$이다. 문제에서 [mm] 로 준 지름을 그대로 쓰면 1,000배가 틀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \pi D N$ — &lt;u&gt;지름을 미터로 바꾼 뒤 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;원주속도 $V = \pi D N$&lt;/strong&gt;&lt;br&gt;단위를 맞추는 것이 전부다. &lt;strong&gt;[m/min] 이면 D를 [m]로&lt;/strong&gt;, &lt;strong&gt;[m/s] 면 &lt;/strong&gt;$\pi D N / 60$이다. 문제에서 [mm]로 준 지름을 그대로 쓰면 1,000배가 틀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = \pi D N$ — &lt;u&gt;지름을 미터로 바꾼 뒤 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="AG49" s="32" t="inlineStr">
         <is>
-          <t>30 [m/min] &lt;strong&gt;미만&lt;/strong&gt;이면 원주의 &lt;strong&gt;1/3 이내&lt;/strong&gt;다. 1/2.5 는 &lt;strong&gt;30 [m/min] 이상&lt;/strong&gt; 일 때다. &lt;strong&gt;느릴수록 더 짧게&lt;/strong&gt; 세워야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;롤러기의 급정지거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;앞면 롤러의 표면속도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;급정지거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;앞면 롤러 원주의 &lt;u&gt;1/3 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;느릴수록 더 짧게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;앞면 롤러 원주의 &lt;u&gt;1/2.5 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>30 [m/min] &lt;strong&gt;미만&lt;/strong&gt;이면 원주의 &lt;strong&gt;1/3 이내&lt;/strong&gt;다. 1/2.5는 &lt;strong&gt;30 [m/min] 이상&lt;/strong&gt;일 때다. &lt;strong&gt;느릴수록 더 짧게&lt;/strong&gt; 세워야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;롤러기의 급정지거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;앞면 롤러의 표면속도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;급정지거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;앞면 롤러 원주의 &lt;u&gt;1/3 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;느릴수록 더 짧게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 [m/min] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;앞면 롤러 원주의 &lt;u&gt;1/2.5 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH49" s="32" t="inlineStr">
@@ -7514,17 +7514,17 @@
       </c>
       <c r="AG50" s="32" t="inlineStr">
         <is>
-          <t>$D = 1 {,} 600 \times T_{m}$ 이다. $1 {,} 600 \times 0.3 = 480$ [mm] = &lt;strong&gt;48 [cm]&lt;/strong&gt;이다.</t>
+          <t>$D = 1 {,} 600 \times T_{m}$이다. $1 {,} 600 \times 0.3 = 480$ [mm] = &lt;strong&gt;48 [cm]&lt;/strong&gt;이다.</t>
         </is>
       </c>
       <c r="AH50" s="32" t="inlineStr">
         <is>
-          <t>② 58 [cm] 는 계산과 맞지 않는다.&lt;br&gt;③ 68 [cm] 도 맞지 않는다.&lt;br&gt;④ 78 [cm] 도 맞지 않는다.</t>
+          <t>② 58 [cm]는 계산과 맞지 않는다.&lt;br&gt;③ 68 [cm] 도 맞지 않는다.&lt;br&gt;④ 78 [cm] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양수조작식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;양수조작식은 &lt;/strong&gt;$D = 1 {,} 600 T_{m}$, &lt;strong&gt;광전자식(감응식)은 &lt;/strong&gt;$D = 1 {,} 600 ( T_{l} + T_{s} )$다. 1,600 [mm/s] 는 &lt;strong&gt;손이 움직이는 속도&lt;/strong&gt;로 잡은 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,600 × 시간&lt;/u&gt; — 답은 [mm] 로 나온다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;양수조작식 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;양수조작식은 &lt;/strong&gt;$D = 1 {,} 600 T_{m}$, &lt;strong&gt;광전자식(감응식)은 &lt;/strong&gt;$D = 1 {,} 600 ( T_{l} + T_{s} )$다. 1,600 [mm/s]는 &lt;strong&gt;손이 움직이는 속도&lt;/strong&gt;로 잡은 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,600 × 시간&lt;/u&gt; — 답은 [mm]로 나온다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="AH52" s="32" t="inlineStr">
         <is>
-          <t>② 1/3 이내는 30 [m/min] 미만일 때다.&lt;br&gt;③ 1/3.5 라는 기준은 없다.&lt;br&gt;④ 1/5.5 라는 기준도 없다.</t>
+          <t>② 1/3 이내는 30 [m/min] 미만일 때다.&lt;br&gt;③ 1/3.5라는 기준은 없다.&lt;br&gt;④ 1/5.5라는 기준도 없다.</t>
         </is>
       </c>
       <c r="AI52" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방호장치 안전인증 고시 — 롤러기 급정지장치의 성능&lt;/strong&gt;&lt;br&gt;앞 문항과 짝이다. &lt;strong&gt;빠르면 1/2.5, 느리면 1/3&lt;/strong&gt; — 값이 커 보이는 쪽이 오히려 여유가 크다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 을 경계로 2.5 와 3&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방호장치 안전인증 고시 — 롤러기 급정지장치의 성능&lt;/strong&gt;&lt;br&gt;앞 문항과 짝이다. &lt;strong&gt;빠르면 1/2.5, 느리면 1/3&lt;/strong&gt; — 값이 커 보이는 쪽이 오히려 여유가 크다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30을 경계로 2.5와 3&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7901,17 +7901,17 @@
       </c>
       <c r="AG53" s="32" t="inlineStr">
         <is>
-          <t>$\text{안전계수} = \text{극한하중} \div \text{정격하중}$ 이므로 $\text{정격하중} = 600 / 4 = 150$ [N] 이다.</t>
+          <t>$\text{안전계수} = \text{극한하중} \div \text{정격하중}$이므로 $\text{정격하중} = 600 / 4 = 150$ [N]이다.</t>
         </is>
       </c>
       <c r="AH53" s="32" t="inlineStr">
         <is>
-          <t>① 130 · 140 은 나눗셈과 맞지 않는다.&lt;br&gt;② 130 · 140 은 나눗셈과 맞지 않는다.&lt;br&gt;④ 160 도 맞지 않는다.</t>
+          <t>① 130 · 140은 나눗셈과 맞지 않는다.&lt;br&gt;② 130 · 140은 나눗셈과 맞지 않는다.&lt;br&gt;④ 160 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI53" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전계수(안전율)&lt;/strong&gt;&lt;br&gt;$S = \dfrac{\text{극한강도}}{\text{허용응력}} = \dfrac{\text{파단하중}}{\text{안전하중}}$ 이다. 양중기 달기구의 안전계수는 &lt;strong&gt;달기 와이어로프 5 · 달기 체인 5 · 훅과 섀클 3 · 섬유로프 등 10&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;극한을 안전계수로 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전계수(안전율)&lt;/strong&gt;&lt;br&gt;$S = \dfrac{\text{극한강도}}{\text{허용응력}} = \dfrac{\text{파단하중}}{\text{안전하중}}$이다. 양중기 달기구의 안전계수는 &lt;strong&gt;달기 와이어로프 5 · 달기 체인 5 · 훅과 섀클 3 · 섬유로프 등 10&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;극한을 안전계수로 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="AI56" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제116조 — 압력방출장치&lt;/strong&gt;&lt;br&gt;검사 뒤에는 &lt;strong&gt;납으로 봉인&lt;/strong&gt; 해 임의로 손대지 못하게 한다. &lt;strong&gt;공정안전보고서 이행수준 평가결과가 우수한 사업장&lt;/strong&gt;은 4년에 1회로 늘릴 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1년에 1회, 우수 사업장은 4년에 1회&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C116%EC%A1%B0" target="_blank"&gt;제116조(압력방출장치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 보일러의 안전한 가동을 위하여 보일러 규격에 맞는 압력방출장치를 1개 또는 2개 이상 설치하고 최고사용압력(설계압력 또는 최고허용압력을 말한다. 이하 같다) 이하에서 작동되도록 하여야 한다. 다만, 압력방출장치가 2개 이상 설치된 경우에는 최고사용압력 이하에서 1개가 작동되고, 다른 압력방출장치는 최고사용압력 1.05배 이하에서 작동되도록 부착하여야 한다.&lt;br&gt;▶ ② 제1항의 &lt;strong&gt;압력방출장치는 매&lt;/strong&gt;년 1회 이상 「국가표준기본법」 제14조제3항에 따라 산업통상부장관의 지정을 받은 국가교정업무 전담기관(이하 "국가교정기관"이라 한다)에서 교정을 받은 압력계를 이용하여 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사한 후 &lt;strong&gt;납으로 봉인&lt;/strong&gt;하여 사용하여야 한다. 다만, 영 제43조에 따른 공정안전보고서 제출 대상으로서 고용노동부장관이 실시하는 공정안전보고서 이행상태 &lt;strong&gt;평가결과가 우수한 사업장&lt;/strong&gt;은 압력방출장치에 대하여 4년마다 1회 이상 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사할 수 있다. &amp;lt;개정 2013.3.23, 2019.12.26, 2025.10.1&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제116조 — 압력방출장치&lt;/strong&gt;&lt;br&gt;검사 뒤에는 &lt;strong&gt;납으로 봉인&lt;/strong&gt;해 임의로 손대지 못하게 한다. &lt;strong&gt;공정안전보고서 이행수준 평가결과가 우수한 사업장&lt;/strong&gt;은 4년에 1회로 늘릴 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1년에 1회, 우수 사업장은 4년에 1회&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C116%EC%A1%B0" target="_blank"&gt;제116조(압력방출장치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 보일러의 안전한 가동을 위하여 보일러 규격에 맞는 압력방출장치를 1개 또는 2개 이상 설치하고 최고사용압력(설계압력 또는 최고허용압력을 말한다. 이하 같다) 이하에서 작동되도록 하여야 한다. 다만, 압력방출장치가 2개 이상 설치된 경우에는 최고사용압력 이하에서 1개가 작동되고, 다른 압력방출장치는 최고사용압력 1.05배 이하에서 작동되도록 부착하여야 한다.&lt;br&gt;▶ ② 제1항의 &lt;strong&gt;압력방출장치는 매&lt;/strong&gt;년 1회 이상 「국가표준기본법」 제14조제3항에 따라 산업통상부장관의 지정을 받은 국가교정업무 전담기관(이하 "국가교정기관"이라 한다)에서 교정을 받은 압력계를 이용하여 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사한 후 &lt;strong&gt;납으로 봉인&lt;/strong&gt;하여 사용하여야 한다. 다만, 영 제43조에 따른 공정안전보고서 제출 대상으로서 고용노동부장관이 실시하는 공정안전보고서 이행상태 &lt;strong&gt;평가결과가 우수한 사업장&lt;/strong&gt;은 압력방출장치에 대하여 4년마다 1회 이상 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사할 수 있다. &amp;lt;개정 2013.3.23, 2019.12.26, 2025.10.1&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -8804,17 +8804,17 @@
       </c>
       <c r="AG60" s="32" t="inlineStr">
         <is>
-          <t>$\text{총 하중} = \text{정하중} + \text{동하중} = m g + m a$ 다. $2 {,} 000 \times 9.8 + 2 {,} 000 \times 10 = 19 {,} 600 + 20 {,} 000 = 39 {,} 600$ [N] = &lt;strong&gt;39.6 [kN]&lt;/strong&gt;이다.</t>
+          <t>$\text{총 하중} = \text{정하중} + \text{동하중} = m g + m a$다. $2 {,} 000 \times 9.8 + 2 {,} 000 \times 10 = 19 {,} 600 + 20 {,} 000 = 39 {,} 600$ [N] = &lt;strong&gt;39.6 [kN]&lt;/strong&gt;이다.</t>
         </is>
       </c>
       <c r="AH60" s="32" t="inlineStr">
         <is>
-          <t>① 9.6 [kN] 은 자릿수가 어긋난다.&lt;br&gt;② 19.6 [kN] 은 정하중만 구한 값이다.&lt;br&gt;③ 29.6 [kN] 은 가속도를 5 로 잡았을 때 쪽이다.</t>
+          <t>① 9.6 [kN]은 자릿수가 어긋난다.&lt;br&gt;② 19.6 [kN]은 정하중만 구한 값이다.&lt;br&gt;③ 29.6 [kN]은 가속도를 5로 잡았을 때 쪽이다.</t>
         </is>
       </c>
       <c r="AI60" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;로프에 걸리는 총 하중&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정하중은 늘 걸리고, 동하중은 올리기 시작할 때만 걸린다&lt;/strong&gt;. 그래서 &lt;strong&gt;감아올리는 순간이 가장 위험&lt;/strong&gt; 하다. 등속으로 오를 때는 정하중뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $W = m ( g + a )$ — &lt;u&gt;가속도를 더한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;로프에 걸리는 총 하중&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정하중은 늘 걸리고, 동하중은 올리기 시작할 때만 걸린다&lt;/strong&gt;. 그래서 &lt;strong&gt;감아올리는 순간이 가장 위험&lt;/strong&gt;하다. 등속으로 오를 때는 정하중뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $W = m ( g + a )$ — &lt;u&gt;가속도를 더한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;기계기구 외함 접지의 생략&lt;/strong&gt;&lt;br&gt;30 [mA] · 0.03초는 &lt;strong&gt;심실세동을 일으키지 않는 한계&lt;/strong&gt;다. 이 값을 넘는 차단기는 접지를 대신할 수 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [mA] · 0.03초&lt;/u&gt; 라야 생략 — 40 [mA] · 2초는 안 된다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;기계기구 외함 접지의 생략&lt;/strong&gt;&lt;br&gt;30 [mA] · 0.03초는 &lt;strong&gt;심실세동을 일으키지 않는 한계&lt;/strong&gt;다. 이 값을 넘는 차단기는 접지를 대신할 수 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [mA] · 0.03초&lt;/u&gt;라야 생략 — 40 [mA] · 2초는 안 된다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9454,12 +9454,12 @@
       </c>
       <c r="AH65" s="32" t="inlineStr">
         <is>
-          <t>① 85 [V] 는 무부하 전압 자체에 가깝다.&lt;br&gt;② 70 [V] 도 무부하 전압대다.&lt;br&gt;③ 50 [V] 는 안전전압 근처이지만 기준값이 아니다.</t>
+          <t>① 85 [V]는 무부하 전압 자체에 가깝다.&lt;br&gt;② 70 [V] 도 무부하 전압대다.&lt;br&gt;③ 50 [V]는 안전전압 근처이지만 기준값이 아니다.</t>
         </is>
       </c>
       <c r="AI65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;교류 아크 용접기의 자동전격방지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1초 이내, 25 [V] 이하&lt;/strong&gt; 두 숫자가 함께 나온다. 습윤한 장소나 철골 위처럼 위험한 곳에서는 &lt;strong&gt;반드시 설치&lt;/strong&gt; 해야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1초 안에 25 [V] 아래로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;교류 아크 용접기의 자동전격방지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1초 이내, 25 [V] 이하&lt;/strong&gt; 두 숫자가 함께 나온다. 습윤한 장소나 철골 위처럼 위험한 곳에서는 &lt;strong&gt;반드시 설치&lt;/strong&gt;해야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1초 안에 25 [V] 아래로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="AH67" s="32" t="inlineStr">
         <is>
-          <t>② 50 [V] 는 네덜란드의 기준이다.&lt;br&gt;③ 60 [V] 는 어느 나라 기준도 아니다.&lt;br&gt;④ 70 [V] 도 마찬가지다.</t>
+          <t>② 50 [V]는 네덜란드의 기준이다.&lt;br&gt;③ 60 [V]는 어느 나라 기준도 아니다.&lt;br&gt;④ 70 [V] 도 마찬가지다.</t>
         </is>
       </c>
       <c r="AI67" s="32" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AG68" s="32" t="inlineStr">
         <is>
-          <t>기준은 &lt;strong&gt;대지전압 150 [V] 를 넘는&lt;/strong&gt; 비충전 금속체다. 100 [V] 가 아니다.</t>
+          <t>기준은 &lt;strong&gt;대지전압 150 [V]를 넘는&lt;/strong&gt; 비충전 금속체다. 100 [V]가 아니다.</t>
         </is>
       </c>
       <c r="AH68" s="32" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;접촉 전위차와 대전열&lt;/strong&gt;&lt;br&gt;이 원리로 물질을 줄 세운 것이 &lt;strong&gt;대전열&lt;/strong&gt;이다. &lt;strong&gt;열에서 멀리 떨어진 두 물질일수록 크게 대전&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;일함수가 다르면 전자가 옮겨간다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;접촉 전위차와 대전열&lt;/strong&gt;&lt;br&gt;이 원리로 물질을 줄 세운 것이 &lt;strong&gt;대전열&lt;/strong&gt;이다. &lt;strong&gt;열에서 멀리 떨어진 두 물질일수록 크게 대전&lt;/strong&gt;된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;일함수가 다르면 전자가 옮겨간다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10078,17 +10078,17 @@
       </c>
       <c r="AG70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;U&lt;/strong&gt;다. &lt;strong&gt;Component(부품)&lt;/strong&gt;를 뜻한다. 그 자체로는 완성품이 아니어서 다른 기기에 조립해 써야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭 인증번호의 접미사&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접미사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 알리나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;U&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방폭부품&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;단독으로 쓸 수 없고 &lt;u&gt;다른 기기에 조립&lt;/u&gt; 해야 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;X&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;특정사용조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 지켜야 할 조건&lt;/u&gt;이 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;없음&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일반&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조건 없이 쓸 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;U&lt;/strong&gt;다. &lt;strong&gt;Component(부품)&lt;/strong&gt;를 뜻한다. 그 자체로는 완성품이 아니어서 다른 기기에 조립해 써야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭 인증번호의 접미사&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접미사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 알리나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;U&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방폭부품&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;단독으로 쓸 수 없고 &lt;u&gt;다른 기기에 조립&lt;/u&gt;해야 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;X&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;특정사용조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 지켜야 할 조건&lt;/u&gt;이 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;없음&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일반&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조건 없이 쓸 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① G 는 가스 분위기를 뜻하는 EPL 앞 글자다.&lt;br&gt;② X 는 특정사용조건이 있음을 나타낸다.&lt;br&gt;③ D 는 분진 분위기를 뜻하는 EPL 앞 글자다.</t>
+          <t>① G는 가스 분위기를 뜻하는 EPL 앞 글자다.&lt;br&gt;② X는 특정사용조건이 있음을 나타낸다.&lt;br&gt;③ D는 분진 분위기를 뜻하는 EPL 앞 글자다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;KS C IEC 60079 — 인증번호의 접미사&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;U 는 부품, X 는 조건&lt;/strong&gt; 둘뿐이다. G·D·M 은 접미사가 아니라 &lt;strong&gt;EPL 의 앞 글자&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;U 는 Unit 이 아니라 부품(Component)&lt;/u&gt; — 조립해 써야 한다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;KS C IEC 60079 — 인증번호의 접미사&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;U는 부품, X는 조건&lt;/strong&gt; 둘뿐이다. G·D·M은 접미사가 아니라 &lt;strong&gt;EPL의 앞 글자&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;U는 Unit이 아니라 부품(Component)&lt;/u&gt; — 조립해 써야 한다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10336,12 +10336,12 @@
       </c>
       <c r="AG72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;T4 의 최고표면온도는 135 [℃]&lt;/strong&gt;다. 150 [℃] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;온도 등급과 최고표면온도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;450 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;135 [℃]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;300 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;100 [℃]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;200 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;85 [℃]&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;T4의 최고표면온도는 135 [℃]&lt;/strong&gt;다. 150 [℃]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;온도 등급과 최고표면온도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;450 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;135 [℃]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;300 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;100 [℃]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;200 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;T6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;85 [℃]&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH72" s="32" t="inlineStr">
         <is>
-          <t>① Ga 는 「매우 높은」 보호등급이 맞다.&lt;br&gt;③ ia 는 본질안전 방폭구조로 0종 장소에 쓸 수 있다.&lt;br&gt;④ ⅡC 는 수소·아세틸렌이 있는 곳에 쓸 수 있다.</t>
+          <t>① Ga는 「매우 높은」 보호등급이 맞다.&lt;br&gt;③ ia는 본질안전 방폭구조로 0종 장소에 쓸 수 있다.&lt;br&gt;④ ⅡC는 수소·아세틸렌이 있는 곳에 쓸 수 있다.</t>
         </is>
       </c>
       <c r="AI72" s="32" t="inlineStr">
@@ -10594,17 +10594,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>$\text{허용사용률} = \dfrac{\text{정격} 2 \text{차전류}^{2}}{\text{실제 용접전류}^{2}} \times \text{정격사용률}$ 이다. $( 300 / 200 )^{2} \times 30 = 2.25 \times 30 = 67.5$ [%] 다.</t>
+          <t>$\text{허용사용률} = \dfrac{\text{정격} 2 \text{차전류}^{2}}{\text{실제 용접전류}^{2}} \times \text{정격사용률}$이다. $( 300 / 200 )^{2} \times 30 = 2.25 \times 30 = 67.5$ [%]다.</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① 13.3 [%] 는 분자와 분모를 뒤바꿨을 때 쪽이다.&lt;br&gt;③ 110.3 [%] 는 제곱하지 않았을 때 나온다.&lt;br&gt;④ 157.5 [%] 도 계산과 맞지 않는다.</t>
+          <t>① 13.3 [%]는 분자와 분모를 뒤바꿨을 때 쪽이다.&lt;br&gt;③ 110.3 [%]는 제곱하지 않았을 때 나온다.&lt;br&gt;④ 157.5 [%] 도 계산과 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;교류아크 용접기의 허용사용률&lt;/strong&gt;&lt;br&gt;발열이 &lt;strong&gt;전류의 제곱에 비례&lt;/strong&gt; 하기 때문에 제곱이 들어간다. &lt;strong&gt;전류를 낮춰 쓰면 더 오래 켜 둘 수 있다&lt;/strong&gt;. 100 [%] 를 넘으면 계속 써도 된다는 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전류비의 제곱을 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;교류아크 용접기의 허용사용률&lt;/strong&gt;&lt;br&gt;발열이 &lt;strong&gt;전류의 제곱에 비례&lt;/strong&gt;하기 때문에 제곱이 들어간다. &lt;strong&gt;전류를 낮춰 쓰면 더 오래 켜 둘 수 있다&lt;/strong&gt;. 100 [%]를 넘으면 계속 써도 된다는 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전류비의 제곱을 곱한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
-          <t>① 0.8 [m] · 1.0 [m] 는 기준에 못 미친다.&lt;br&gt;③ 2.0 [m] · 3.0 [m] 는 기준보다 크게 잡은 값이다.&lt;br&gt;④ 3.5 [m] · 4.0 [m] 도 기준이 아니다.</t>
+          <t>① 0.8 [m] · 1.0 [m]는 기준에 못 미친다.&lt;br&gt;③ 2.0 [m] · 3.0 [m]는 기준보다 크게 잡은 값이다.&lt;br&gt;④ 3.5 [m] · 4.0 [m] 도 기준이 아니다.</t>
         </is>
       </c>
       <c r="AI75" s="32" t="inlineStr">
@@ -10966,7 +10966,7 @@
       <c r="AA77" s="32" t="inlineStr"/>
       <c r="AB77" s="32" t="inlineStr">
         <is>
-          <t>전로의 사용전압이 FELV 일 때 DC 시험 전압은 500 V 이다</t>
+          <t>전로의 사용전압이 FELV 일 때 DC 시험 전압은 500 V이다</t>
         </is>
       </c>
       <c r="AC77" s="32" t="inlineStr"/>
@@ -10981,17 +10981,17 @@
       </c>
       <c r="AG77" s="32" t="inlineStr">
         <is>
-          <t>500 [V] 를 넘는 전로의 절연저항은 &lt;strong&gt;1.0 [MΩ] 이상&lt;/strong&gt;이다. 1.5 [MΩ] 이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;저압전로의 절연저항 (KEC 132)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전로의 사용전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;DC 시험전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;절연저항&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;SELV 및 PELV&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;250 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.5 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FELV, 500 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;500 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;500 [V] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>500 [V]를 넘는 전로의 절연저항은 &lt;strong&gt;1.0 [MΩ] 이상&lt;/strong&gt;이다. 1.5 [MΩ]이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;저압전로의 절연저항 (KEC 132)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전로의 사용전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;DC 시험전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;절연저항&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;SELV 및 PELV&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;250 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.5 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FELV, 500 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;500 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;500 [V] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000 [V]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH77" s="32" t="inlineStr">
         <is>
-          <t>① SELV·PELV 는 0.5 [MΩ] 이상이 맞다.&lt;br&gt;② FELV 는 1 [MΩ] 이상이 맞다.&lt;br&gt;③ FELV 의 DC 시험전압 500 [V] 도 맞다.</t>
+          <t>① SELV·PELV는 0.5 [MΩ] 이상이 맞다.&lt;br&gt;② FELV는 1 [MΩ] 이상이 맞다.&lt;br&gt;③ FELV의 DC 시험전압 500 [V] 도 맞다.</t>
         </is>
       </c>
       <c r="AI77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;한국전기설비규정(KEC) 132 — 전로의 절연저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;500 [V] 를 넘어도 절연저항은 1.0 [MΩ] 그대로&lt;/strong&gt;이고 &lt;strong&gt;시험전압만 1,000 [V] 로 올라간다&lt;/strong&gt;. 여기가 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.5 · 1.0 · 1.0&lt;/u&gt; — 저항은 1.0 에서 멈춘다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 옛 기준(전기설비기술기준)은 대지전압 &lt;u&gt;150 [V] 이하 0.1 [MΩ]&lt;/u&gt;, &lt;u&gt;300 [V] 이하 0.2 [MΩ]&lt;/u&gt; 식으로 나뉘어 있었으나, &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 위 표처럼 바뀌었다. 옛 숫자를 외우고 있으면 틀린다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;한국전기설비규정(KEC) 132 — 전로의 절연저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;500 [V]를 넘어도 절연저항은 1.0 [MΩ] 그대로&lt;/strong&gt;이고 &lt;strong&gt;시험전압만 1,000 [V]로 올라간다&lt;/strong&gt;. 여기가 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.5 · 1.0 · 1.0&lt;/u&gt; — 저항은 1.0에서 멈춘다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 옛 기준(전기설비기술기준)은 대지전압 &lt;u&gt;150 [V] 이하 0.1 [MΩ]&lt;/u&gt;, &lt;u&gt;300 [V] 이하 0.2 [MΩ]&lt;/u&gt; 식으로 나뉘어 있었으나, &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 위 표처럼 바뀌었다. 옛 숫자를 외우고 있으면 틀린다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11249,7 +11249,7 @@
       </c>
       <c r="AI79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인체 대전의 방지대책&lt;/strong&gt;&lt;br&gt;네 가지 모두 &lt;strong&gt;전하가 빠져나갈 길을 만드는&lt;/strong&gt; 일이다. 손목 접지대·제전복·정전화·도전성 바닥이 모두 그렇다. &lt;strong&gt;저항이 클수록 위험&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;길을 터 준다&lt;/u&gt; — 막으면 쌓인다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인체 대전의 방지대책&lt;/strong&gt;&lt;br&gt;네 가지 모두 &lt;strong&gt;전하가 빠져나갈 길을 만드는&lt;/strong&gt; 일이다. 손목 접지대·제전복·정전화·도전성 바닥이 모두 그렇다. &lt;strong&gt;저항이 클수록 위험&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;길을 터 준다&lt;/u&gt; — 막으면 쌓인다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="AG80" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「IN 계통」이라는 것은 없다&lt;/strong&gt;. 계통접지는 &lt;strong&gt;TN · TT · IT&lt;/strong&gt; 셋뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;계통접지의 세 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;계통&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전원 측 / 노출도전부&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;TN&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직접 접지 / 전원 접지에 연결&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;TN-S · TN-C · TN-C-S 로 나뉜다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;TT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직접 접지 / 따로 접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;각자 접지&lt;/u&gt; — 우리나라 저압 배전에 많다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비접지 또는 고임피던스 / 따로 접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1선 지락에도 계속 운전&lt;/u&gt; — 병원·화학공장&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「IN 계통」이라는 것은 없다&lt;/strong&gt;. 계통접지는 &lt;strong&gt;TN · TT · IT&lt;/strong&gt; 셋뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;계통접지의 세 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;계통&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전원 측 / 노출도전부&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;TN&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직접 접지 / 전원 접지에 연결&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;TN-S · TN-C · TN-C-S로 나뉜다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;TT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직접 접지 / 따로 접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;각자 접지&lt;/u&gt; — 우리나라 저압 배전에 많다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;비접지 또는 고임피던스 / 따로 접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1선 지락에도 계속 운전&lt;/u&gt; — 병원·화학공장&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH80" s="32" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="AI80" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;계통접지의 분류&lt;/strong&gt;&lt;br&gt;첫 글자는 &lt;strong&gt;전원 측(T 접지 · I 비접지)&lt;/strong&gt;, 둘째 글자는 &lt;strong&gt;노출도전부(T 따로 접지 · N 전원 접지에 연결)&lt;/strong&gt;를 뜻한다. 그래서 &lt;strong&gt;IN 이라는 조합은 성립하지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;TN · TT · IT&lt;/u&gt; — IN 은 없다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;계통접지의 분류&lt;/strong&gt;&lt;br&gt;첫 글자는 &lt;strong&gt;전원 측(T 접지 · I 비접지)&lt;/strong&gt;, 둘째 글자는 &lt;strong&gt;노출도전부(T 따로 접지 · N 전원 접지에 연결)&lt;/strong&gt;를 뜻한다. 그래서 &lt;strong&gt;IN이라는 조합은 성립하지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;TN · TT · IT&lt;/u&gt; — IN은 없다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="U82" s="32" t="inlineStr">
         <is>
-          <t>Q = 2X10-7 C 으로 대전하고 있는 반경 25 cm 도체구의 전위(kV)는 약 얼마인가?</t>
+          <t>Q = 2X10-7 C으로 대전하고 있는 반경 25 cm 도체구의 전위(kV)는 약 얼마인가?</t>
         </is>
       </c>
       <c r="V82" s="32" t="inlineStr"/>
@@ -11626,17 +11626,17 @@
       </c>
       <c r="AG82" s="32" t="inlineStr">
         <is>
-          <t>도체구의 전위는 $V = \dfrac{1}{4 \pi \varepsilon_{0}} \times \dfrac{Q}{r} = 9 \times 10^{9} \times \dfrac{Q}{r}$ 다. $9 \times 10^{9} \times 2 \times 10^{-7} / 0.25 = 1 {,} 800 / 0.25 = 7 {,} 200$ [V] = &lt;strong&gt;7.2 [kV]&lt;/strong&gt;다.</t>
+          <t>도체구의 전위는 $V = \dfrac{1}{4 \pi \varepsilon_{0}} \times \dfrac{Q}{r} = 9 \times 10^{9} \times \dfrac{Q}{r}$다. $9 \times 10^{9} \times 2 \times 10^{-7} / 0.25 = 1 {,} 800 / 0.25 = 7 {,} 200$ [V] = &lt;strong&gt;7.2 [kV]&lt;/strong&gt;다.</t>
         </is>
       </c>
       <c r="AH82" s="32" t="inlineStr">
         <is>
-          <t>② 12.5 [kV] 는 계산과 맞지 않는다.&lt;br&gt;③ 14.4 [kV] 는 반지름 대신 지름을 썼을 때 쪽이다.&lt;br&gt;④ 25 [kV] 도 맞지 않는다.</t>
+          <t>② 12.5 [kV]는 계산과 맞지 않는다.&lt;br&gt;③ 14.4 [kV]는 반지름 대신 지름을 썼을 때 쪽이다.&lt;br&gt;④ 25 [kV] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI82" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;도체구의 전위&lt;/strong&gt;&lt;br&gt;$9 \times 10^{9}$ 은 쿨롱 상수 $1 / 4 \pi \varepsilon_{0}$ 다. &lt;strong&gt;반지름을 [m] 로 바꾸는 것&lt;/strong&gt;이 실수하기 쉬운 자리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = 9 \times 10^{9} Q / r$ — &lt;u&gt;반지름은 미터로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;도체구의 전위&lt;/strong&gt;&lt;br&gt;$9 \times 10^{9}$은 쿨롱 상수 $1 / 4 \pi \varepsilon_{0}$다. &lt;strong&gt;반지름을 [m]로 바꾸는 것&lt;/strong&gt;이 실수하기 쉬운 자리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = 9 \times 10^{9} Q / r$ — &lt;u&gt;반지름은 미터로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11868,7 +11868,7 @@
       </c>
       <c r="AG84" s="32" t="inlineStr">
         <is>
-          <t>메탄올의 비중은 &lt;strong&gt;0.79 로 1보다 작다&lt;/strong&gt;. 증기비중은 &lt;strong&gt;1.11 로 공기보다 무겁다&lt;/strong&gt;. 두 군데가 다 거꾸로다.</t>
+          <t>메탄올의 비중은 &lt;strong&gt;0.79로 1보다 작다&lt;/strong&gt;. 증기비중은 &lt;strong&gt;1.11로 공기보다 무겁다&lt;/strong&gt;. 두 군데가 다 거꾸로다.</t>
         </is>
       </c>
       <c r="AH84" s="32" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;메탄올(CH₃OH)의 성질&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;액체의 비중은 물(1) 기준&lt;/strong&gt;, &lt;strong&gt;증기비중은 공기(29) 기준&lt;/strong&gt;이다. 메탄올의 분자량이 32 이므로 $32 / 29 = 1.1$ 로 공기보다 무겁다. &lt;strong&gt;대부분의 유기용제 증기는 공기보다 무거워 바닥에 깔린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;액체는 가볍고, 증기는 무겁다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;메탄올(CH₃OH)의 성질&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;액체의 비중은 물(1) 기준&lt;/strong&gt;, &lt;strong&gt;증기비중은 공기(29) 기준&lt;/strong&gt;이다. 메탄올의 분자량이 32이므로 $32 / 29 = 1.1$로 공기보다 무겁다. &lt;strong&gt;대부분의 유기용제 증기는 공기보다 무거워 바닥에 깔린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;액체는 가볍고, 증기는 무겁다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;기상폭발과 응상폭발&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기상폭발&lt;/strong&gt;은 혼합가스 · 분진 · 분무 · &lt;strong&gt;분해&lt;/strong&gt; · 증기운(UVCE) 이고, &lt;strong&gt;응상폭발&lt;/strong&gt;은 &lt;strong&gt;수증기폭발 · 증기폭발 · 전선폭발 · 고상 간 전이&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분해폭발만 기상&lt;/u&gt; — 나머지 셋은 응상.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;기상폭발과 응상폭발&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기상폭발&lt;/strong&gt;은 혼합가스 · 분진 · 분무 · &lt;strong&gt;분해&lt;/strong&gt; · 증기운(UVCE)이고, &lt;strong&gt;응상폭발&lt;/strong&gt;은 &lt;strong&gt;수증기폭발 · 증기폭발 · 전선폭발 · 고상 간 전이&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분해폭발만 기상&lt;/u&gt; — 나머지 셋은 응상.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12642,12 +12642,12 @@
       </c>
       <c r="AG90" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;이황화탄소가 −30 [℃]&lt;/strong&gt;로 가장 낮다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 물질의 인화점&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인화점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;디에틸에테르&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−45 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 낮은 축&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이황화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−30 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물속에 저장&lt;/u&gt; 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산화프로필렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;−37 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세톤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;−18 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄올&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;11 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0 [℃] 보다 높다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크실렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;약 25 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 ~ 70 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제2석유류&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;이황화탄소가 −30 [℃]&lt;/strong&gt;로 가장 낮다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 물질의 인화점&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;인화점&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;디에틸에테르&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−45 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 낮은 축&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이황화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−30 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물속에 저장&lt;/u&gt;한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산화프로필렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;−37 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세톤&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;−18 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄올&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;11 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0 [℃]보다 높다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크실렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;약 25 [℃]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 ~ 70 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제2석유류&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH90" s="32" t="inlineStr">
         <is>
-          <t>② 아세톤은 −18 [℃] 다.&lt;br&gt;③ 크실렌은 약 25 [℃] 다.&lt;br&gt;④ 경유는 50 ~ 70 [℃] 다.</t>
+          <t>② 아세톤은 −18 [℃]다.&lt;br&gt;③ 크실렌은 약 25 [℃]다.&lt;br&gt;④ 경유는 50 ~ 70 [℃]다.</t>
         </is>
       </c>
       <c r="AI90" s="32" t="inlineStr">
@@ -12904,12 +12904,12 @@
       </c>
       <c r="AG92" s="32" t="inlineStr">
         <is>
-          <t>모두 &lt;strong&gt;물반응성 물질 및 인화성 고체&lt;/strong&gt;다. 리튬·칼륨·나트륨은 &lt;strong&gt;물과 만나면 수소를 내며 발열&lt;/strong&gt; 하고, 황·황린·황화인·적린은 &lt;strong&gt;쉽게 불이 붙는 고체&lt;/strong&gt;다.</t>
+          <t>모두 &lt;strong&gt;물반응성 물질 및 인화성 고체&lt;/strong&gt;다. 리튬·칼륨·나트륨은 &lt;strong&gt;물과 만나면 수소를 내며 발열&lt;/strong&gt;하고, 황·황린·황화인·적린은 &lt;strong&gt;쉽게 불이 붙는 고체&lt;/strong&gt;다.</t>
         </is>
       </c>
       <c r="AH92" s="32" t="inlineStr">
         <is>
-          <t>① 폭발성 물질은 질산에스테르류·니트로화합물 등이다.&lt;br&gt;② 산화성 물질은 염소산·과염소산·과산화물 등이다.&lt;br&gt;④ 급성 독성 물질은 LD50 이 일정 값 이하인 물질이다.</t>
+          <t>① 폭발성 물질은 질산에스테르류·니트로화합물 등이다.&lt;br&gt;② 산화성 물질은 염소산·과염소산·과산화물 등이다.&lt;br&gt;④ 급성 독성 물질은 LD50이 일정 값 이하인 물질이다.</t>
         </is>
       </c>
       <c r="AI92" s="32" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="AG96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;강화액 소화약제&lt;/strong&gt;다. 탄산칼륨을 녹여 &lt;strong&gt;어는점을 −20 [℃] 까지 낮추고&lt;/strong&gt; 소화력도 높였다.</t>
+          <t>&lt;strong&gt;강화액 소화약제&lt;/strong&gt;다. 탄산칼륨을 녹여 &lt;strong&gt;어는점을 −20 [℃]까지 낮추고&lt;/strong&gt; 소화력도 높였다.</t>
         </is>
       </c>
       <c r="AH96" s="32" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;일산화탄소는 그 자체가 가연성 가스&lt;/strong&gt;다. 폭발범위가 12.5~74 [%] 로 넓어 오히려 위험을 키운다.</t>
+          <t>&lt;strong&gt;일산화탄소는 그 자체가 가연성 가스&lt;/strong&gt;다. 폭발범위가 12.5~74 [%]로 넓어 오히려 위험을 키운다.</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="AI100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;불활성화(퍼지)&lt;/strong&gt;&lt;br&gt;목표는 산소농도를 &lt;strong&gt;최소산소농도(MOC) 아래&lt;/strong&gt;로 낮추는 것이다. 안전을 위해 &lt;strong&gt;MOC 보다 4 [%] 정도 더 낮게&lt;/strong&gt; 잡는다. $\mathrm{MOC} = \text{폭발하한계} \times \text{산소의 양론계수}$ 로 어림한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;타는 기체는 불활성 가스가 될 수 없다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;불활성화(퍼지)&lt;/strong&gt;&lt;br&gt;목표는 산소농도를 &lt;strong&gt;최소산소농도(MOC) 아래&lt;/strong&gt;로 낮추는 것이다. 안전을 위해 &lt;strong&gt;MOC보다 4 [%] 정도 더 낮게&lt;/strong&gt; 잡는다. $\mathrm{MOC} = \text{폭발하한계} \times \text{산소의 양론계수}$로 어림한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;타는 기체는 불활성 가스가 될 수 없다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14065,12 +14065,12 @@
       </c>
       <c r="AG101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;메탄올의 인화점은 11 [℃]&lt;/strong&gt;로 0 [℃] 보다 높다. 나머지 셋은 모두 영하다.</t>
+          <t>&lt;strong&gt;메탄올의 인화점은 11 [℃]&lt;/strong&gt;로 0 [℃]보다 높다. 나머지 셋은 모두 영하다.</t>
         </is>
       </c>
       <c r="AH101" s="32" t="inlineStr">
         <is>
-          <t>② 이황화탄소는 −30 [℃] 다.&lt;br&gt;③ 산화프로필렌은 −37 [℃] 다.&lt;br&gt;④ 디에틸에테르는 −45 [℃] 다.</t>
+          <t>② 이황화탄소는 −30 [℃]다.&lt;br&gt;③ 산화프로필렌은 −37 [℃]다.&lt;br&gt;④ 디에틸에테르는 −45 [℃]다.</t>
         </is>
       </c>
       <c r="AI101" s="32" t="inlineStr">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="AI103" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제23조 — 가설통로의 구조&lt;/strong&gt;&lt;br&gt;가설통로의 숫자는 넷이다 — &lt;strong&gt;경사 30° 이하 · 15° 초과 시 미끄럼 방지 · 높이 8 [m] 이상인 비계다리는 7 [m] 이내마다 계단참 · 수직갱 길이 15 [m] 이상이면 10 [m] 이내마다 계단참&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 은 한도, 15 는 미끄럼&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C23%EC%A1%B0" target="_blank"&gt;제23조(가설통로의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 가설통로를 설치하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt; 2. 경사는 30도 이하로 할 것. 다만, 계단을 설치하거나 높이 2미터 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 경사가 15도를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것&lt;br&gt; 4. 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.&lt;br&gt;▶  5. 수직갱에 가설된 통로의 길이가 15미터 이상인 경우에는 10미터 &lt;strong&gt;이내마다 계단참&lt;/strong&gt;을 설치할 것&lt;br&gt;▶  6. 건설공사에 사용하는 높이 8미터 이상인 비계다리에는 7미터 &lt;strong&gt;이내마다 계단참&lt;/strong&gt;을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제23조 — 가설통로의 구조&lt;/strong&gt;&lt;br&gt;가설통로의 숫자는 넷이다 — &lt;strong&gt;경사 30° 이하 · 15° 초과 시 미끄럼 방지 · 높이 8 [m] 이상인 비계다리는 7 [m] 이내마다 계단참 · 수직갱 길이 15 [m] 이상이면 10 [m] 이내마다 계단참&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30은 한도, 15는 미끄럼&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C23%EC%A1%B0" target="_blank"&gt;제23조(가설통로의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 가설통로를 설치하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt; 2. 경사는 30도 이하로 할 것. 다만, 계단을 설치하거나 높이 2미터 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 경사가 15도를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것&lt;br&gt; 4. 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.&lt;br&gt;▶  5. 수직갱에 가설된 통로의 길이가 15미터 이상인 경우에는 10미터 &lt;strong&gt;이내마다 계단참&lt;/strong&gt;을 설치할 것&lt;br&gt;▶  6. 건설공사에 사용하는 높이 8미터 이상인 비계다리에는 7미터 &lt;strong&gt;이내마다 계단참&lt;/strong&gt;을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -14452,17 +14452,17 @@
       </c>
       <c r="AG104" s="32" t="inlineStr">
         <is>
-          <t>$\text{허용응력} = \text{인장강도} \div \text{안전계수} = 2 {,} 000 / 4 = 500$ [MPa] 이다.</t>
+          <t>$\text{허용응력} = \text{인장강도} \div \text{안전계수} = 2 {,} 000 / 4 = 500$ [MPa]이다.</t>
         </is>
       </c>
       <c r="AH104" s="32" t="inlineStr">
         <is>
-          <t>② 1,000 [MPa] 은 안전계수를 2 로 잡았을 때다.&lt;br&gt;③ 1,500 [MPa] 도 계산과 맞지 않는다.&lt;br&gt;④ 2,000 [MPa] 은 인장강도 자체다.</t>
+          <t>② 1,000 [MPa]은 안전계수를 2로 잡았을 때다.&lt;br&gt;③ 1,500 [MPa] 도 계산과 맞지 않는다.&lt;br&gt;④ 2,000 [MPa]은 인장강도 자체다.</t>
         </is>
       </c>
       <c r="AI104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전계수(안전율)&lt;/strong&gt;&lt;br&gt;$S = \dfrac{\text{극한강도}}{\text{허용응력}}$ 이므로 &lt;strong&gt;안전계수가 클수록 허용응력은 작아진다&lt;/strong&gt;. 더 여유 있게 쓰겠다는 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;강도를 안전계수로 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전계수(안전율)&lt;/strong&gt;&lt;br&gt;$S = \dfrac{\text{극한강도}}{\text{허용응력}}$이므로 &lt;strong&gt;안전계수가 클수록 허용응력은 작아진다&lt;/strong&gt;. 더 여유 있게 쓰겠다는 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;강도를 안전계수로 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14710,7 +14710,7 @@
       </c>
       <c r="AG106" s="32" t="inlineStr">
         <is>
-          <t>수직갱은 &lt;strong&gt;15 [m] 이상이면 10 [m] 이내마다&lt;/strong&gt; 계단참을 둔다. 7 [m] 는 &lt;strong&gt;건설공사용 비계다리(높이 8 [m] 이상)&lt;/strong&gt;의 기준이다. 두 기준이 뒤바뀐 보기다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가설통로의 계단참&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;어디&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;계단참 간격&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수직갱에 가설된 통로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;길이 &lt;u&gt;15 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 이내마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건설공사용 비계다리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;높이 &lt;u&gt;8 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7 [m] 이내마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>수직갱은 &lt;strong&gt;15 [m] 이상이면 10 [m] 이내마다&lt;/strong&gt; 계단참을 둔다. 7 [m]는 &lt;strong&gt;건설공사용 비계다리(높이 8 [m] 이상)&lt;/strong&gt;의 기준이다. 두 기준이 뒤바뀐 보기다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가설통로의 계단참&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;어디&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;계단참 간격&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수직갱에 가설된 통로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;길이 &lt;u&gt;15 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 이내마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건설공사용 비계다리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;높이 &lt;u&gt;8 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;7 [m] 이내마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH106" s="32" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="AI106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제23조 — 가설통로의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;15 와 10 이 짝, 8 과 7 이 짝&lt;/strong&gt;이다. 숫자를 짝으로 묶어 외우면 뒤바꾼 보기를 바로 잡아낸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수직갱 15 → 10, 비계다리 8 → 7&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C23%EC%A1%B0" target="_blank"&gt;제23조(가설통로의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 가설통로를 설치하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt; 2. 경사는 30도 이하로 할 것. 다만, 계단을 설치하거나 높이 2미터 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 경사가 15도를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것&lt;br&gt; 4. 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.&lt;br&gt;▶  5. &lt;strong&gt;수직갱에 가설된 통로의 길이가&lt;/strong&gt; 15미터 이상인 경우에는 10미터 이내마다 계단참을 설치할 것&lt;br&gt; 6. 건설공사에 사용하는 높이 8미터 이상인 비계다리에는 7미터 이내마다 계단참을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제23조 — 가설통로의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;15와 10이 짝, 8과 7이 짝&lt;/strong&gt;이다. 숫자를 짝으로 묶어 외우면 뒤바꾼 보기를 바로 잡아낸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수직갱 15 → 10, 비계다리 8 → 7&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C23%EC%A1%B0" target="_blank"&gt;제23조(가설통로의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 가설통로를 설치하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt; 2. 경사는 30도 이하로 할 것. 다만, 계단을 설치하거나 높이 2미터 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 경사가 15도를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것&lt;br&gt; 4. 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.&lt;br&gt;▶  5. &lt;strong&gt;수직갱에 가설된 통로의 길이가&lt;/strong&gt; 15미터 이상인 경우에는 10미터 이내마다 계단참을 설치할 것&lt;br&gt; 6. 건설공사에 사용하는 높이 8미터 이상인 비계다리에는 7미터 이내마다 계단참을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="AI108" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;액상화(liquefaction)&lt;/strong&gt;&lt;br&gt;느슨한 &lt;strong&gt;포화 사질토&lt;/strong&gt;에 진동이 가해지면 &lt;strong&gt;간극수압이 급격히 올라 유효응력이 0 이 되어&lt;/strong&gt; 흙이 액체처럼 흐른다. 대책은 두 갈래 — &lt;strong&gt;물을 빼거나(웰포인트·배수) 흙을 조이거나(동다짐·다짐말뚝)&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;물이 문제면 물을 뺀다&lt;/u&gt; — 웰포인트.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;액상화(liquefaction)&lt;/strong&gt;&lt;br&gt;느슨한 &lt;strong&gt;포화 사질토&lt;/strong&gt;에 진동이 가해지면 &lt;strong&gt;간극수압이 급격히 올라 유효응력이 0이 되어&lt;/strong&gt; 흙이 액체처럼 흐른다. 대책은 두 갈래 — &lt;strong&gt;물을 빼거나(웰포인트·배수) 흙을 조이거나(동다짐·다짐말뚝)&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;물이 문제면 물을 뺀다&lt;/u&gt; — 웰포인트.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15102,7 @@
       </c>
       <c r="AH109" s="32" t="inlineStr">
         <is>
-          <t>① 50 [%] 는 기준이 아니다.&lt;br&gt;② 60 [%] 도 아니다.&lt;br&gt;④ 80 [%] 도 아니다.</t>
+          <t>① 50 [%]는 기준이 아니다.&lt;br&gt;② 60 [%] 도 아니다.&lt;br&gt;④ 80 [%] 도 아니다.</t>
         </is>
       </c>
       <c r="AI109" s="32" t="inlineStr">
@@ -15613,12 +15613,12 @@
       </c>
       <c r="AG113" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;N 치 4~10 은 「느슨함」&lt;/strong&gt;이다. 매우 단단한 것은 &lt;strong&gt;N 치 50 이상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;N 치와 모래의 상대밀도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;N 치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상대밀도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0 ~ 4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매우 느슨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;액상화 위험&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4 ~ 10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느슨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항의 답&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 ~ 30&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보통&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조밀한 편&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 ~ 50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조밀&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매우 조밀&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;N 치 4~10은 「느슨함」&lt;/strong&gt;이다. 매우 단단한 것은 &lt;strong&gt;N 치 50 이상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;N 치와 모래의 상대밀도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;N 치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상대밀도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0 ~ 4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매우 느슨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;액상화 위험&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4 ~ 10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느슨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항의 답&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 ~ 30&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보통&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조밀한 편&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;30 ~ 50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;조밀&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매우 조밀&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH113" s="32" t="inlineStr">
         <is>
-          <t>① N 치는 30 [cm] 굴진에 필요한 타격횟수가 맞다.&lt;br&gt;③ 63.5 [kg] 추를 76 [cm] 에서 떨어뜨리는 것이 맞다.&lt;br&gt;④ 사질지반에 쓰며 점토지반에서는 신뢰성이 떨어지는 것이 맞다.</t>
+          <t>① N 치는 30 [cm] 굴진에 필요한 타격횟수가 맞다.&lt;br&gt;③ 63.5 [kg] 추를 76 [cm]에서 떨어뜨리는 것이 맞다.&lt;br&gt;④ 사질지반에 쓰며 점토지반에서는 신뢰성이 떨어지는 것이 맞다.</t>
         </is>
       </c>
       <c r="AI113" s="32" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="AG114" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;추락방호망&lt;/strong&gt;이다. 작업발판을 놓기 어려운 곳에서 &lt;strong&gt;떨어지는 사람을 받아 낸다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;추락방호망의 설치 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;설치 높이&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업면에서 &lt;u&gt;10 [m] 를 초과하지 않게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가까울수록 좋다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;수평면과의 각도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20° ~ 30°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;내민 길이&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;벽면에서 &lt;u&gt;3 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;처짐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;짧은 변 길이의 &lt;u&gt;12 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;추락방호망&lt;/strong&gt;이다. 작업발판을 놓기 어려운 곳에서 &lt;strong&gt;떨어지는 사람을 받아 낸다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;추락방호망의 설치 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;설치 높이&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업면에서 &lt;u&gt;10 [m]를 초과하지 않게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가까울수록 좋다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;수평면과의 각도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20° ~ 30°&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;내민 길이&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;벽면에서 &lt;u&gt;3 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;처짐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;짧은 변 길이의 &lt;u&gt;12 [%] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH114" s="32" t="inlineStr">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="AH116" s="32" t="inlineStr">
         <is>
-          <t>① 문화재 0.2 [cm/s] 는 맞다.&lt;br&gt;② 주택·아파트 0.5 [cm/s] 도 맞다.&lt;br&gt;③ 상가 1.0 [cm/s] 도 맞다.</t>
+          <t>① 문화재 0.2 [cm/s]는 맞다.&lt;br&gt;② 주택·아파트 0.5 [cm/s] 도 맞다.&lt;br&gt;③ 상가 1.0 [cm/s] 도 맞다.</t>
         </is>
       </c>
       <c r="AI116" s="32" t="inlineStr">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="AG118" s="32" t="inlineStr">
         <is>
-          <t>초정밀작업은 &lt;strong&gt;750 [lux] 이상&lt;/strong&gt;이다. 600 이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업면의 조도기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;작업&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;초정밀작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;750 [lux] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항의 답&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정밀작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [lux] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보통작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;150 [lux] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖의 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75 [lux] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>초정밀작업은 &lt;strong&gt;750 [lux] 이상&lt;/strong&gt;이다. 600이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업면의 조도기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;작업&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;초정밀작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;750 [lux] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항의 답&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정밀작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [lux] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보통작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;150 [lux] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖의 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75 [lux] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH118" s="32" t="inlineStr">
@@ -16650,12 +16650,12 @@
       </c>
       <c r="AH121" s="32" t="inlineStr">
         <is>
-          <t>① 1 : 0.3 은 어느 기준에도 없다.&lt;br&gt;② 1 : 0.4 도 없다.&lt;br&gt;④ 1 : 0.6 도 없다.</t>
+          <t>① 1 : 0.3은 어느 기준에도 없다.&lt;br&gt;② 1 : 0.4 도 없다.&lt;br&gt;④ 1 : 0.6 도 없다.</t>
         </is>
       </c>
       <c r="AI121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 별표11 — 굴착면의 기울기 기준&lt;/strong&gt;&lt;br&gt;현행 기준은 네 줄로 단순해졌다 — &lt;strong&gt;모래 1:1.8 · 연암 및 풍화암 1:1.0 · 경암 1:0.5 · 그 밖의 흙 1:1.2&lt;/strong&gt;. &lt;strong&gt;연암이 1:0.5 에서 1:1.0 으로 완만해진 것&lt;/strong&gt;이 가장 큰 변화다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1.8 · 1.0 · 0.5 · 1.2&lt;/u&gt; — 모래 · 연암풍화암 · 경암 · 그 밖의 흙.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 이 문항은 &lt;u&gt;개정 전 기준&lt;/u&gt;으로 출제되어 가답안이 ③(1 : 0.5)이다. &lt;u&gt;2021. 11. 19. 개정&lt;/u&gt;으로 &lt;u&gt;연암과 풍화암이 하나로 묶여 1 : 1.0&lt;/u&gt;이 되었으므로, &lt;u&gt;현행 기준으로는 ③이 오답&lt;/u&gt;이다. 지금 시험을 본다면 &lt;u&gt;1 : 1.0&lt;/u&gt;을 골라야 한다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 11&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 별표11 — 굴착면의 기울기 기준&lt;/strong&gt;&lt;br&gt;현행 기준은 네 줄로 단순해졌다 — &lt;strong&gt;모래 1:1.8 · 연암 및 풍화암 1:1.0 · 경암 1:0.5 · 그 밖의 흙 1:1.2&lt;/strong&gt;. &lt;strong&gt;연암이 1:0.5에서 1:1.0으로 완만해진 것&lt;/strong&gt;이 가장 큰 변화다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1.8 · 1.0 · 0.5 · 1.2&lt;/u&gt; — 모래 · 연암풍화암 · 경암 · 그 밖의 흙.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 이 문항은 &lt;u&gt;개정 전 기준&lt;/u&gt;으로 출제되어 가답안이 ③(1 : 0.5)이다. &lt;u&gt;2021. 11. 19. 개정&lt;/u&gt;으로 &lt;u&gt;연암과 풍화암이 하나로 묶여 1 : 1.0&lt;/u&gt;이 되었으므로, &lt;u&gt;현행 기준으로는 ③이 오답&lt;/u&gt;이다. 지금 시험을 본다면 &lt;u&gt;1 : 1.0&lt;/u&gt;을 골라야 한다.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 11&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
         </is>
       </c>
     </row>
